--- a/data/lossofsale_sg_chavakkad.xlsx
+++ b/data/lossofsale_sg_chavakkad.xlsx
@@ -1424,6 +1424,102 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="65">
+        <v>23</v>
+      </c>
+      <c t="inlineStr" r="B25">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C25">
+        <is>
+          <t xml:space="preserve">aswith</t>
+        </is>
+      </c>
+      <c r="D25" s="65">
+        <v>9656182795</v>
+      </c>
+      <c t="inlineStr" r="E25">
+        <is>
+          <t xml:space="preserve">08-02-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F25">
+        <is>
+          <t xml:space="preserve">MAHESH C</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G25">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H25">
+        <is>
+          <t xml:space="preserve">SIZE NOT SUITABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I25">
+        <is>
+          <t xml:space="preserve">SIZE TOO LARGE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J25">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="65">
+        <v>24</v>
+      </c>
+      <c t="inlineStr" r="B26">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C26">
+        <is>
+          <t xml:space="preserve">nahil</t>
+        </is>
+      </c>
+      <c r="D26" s="65">
+        <v>9605808064</v>
+      </c>
+      <c t="inlineStr" r="E26">
+        <is>
+          <t xml:space="preserve">10-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F26">
+        <is>
+          <t xml:space="preserve">RASAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G26">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H26">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I26">
+        <is>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J26">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
